--- a/Zinc/5. Cluster analysis/Typology Plots/Relative_freq_percentages_by_cluster.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Relative_freq_percentages_by_cluster.xlsx
@@ -1,92 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/5. Cluster analysis/Typology Plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_C2CE303C0039E0D79C47B8CE6FF01514B2D7A973" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE84CC9A-4FDC-4468-B1AF-D51F416717CF}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="19">
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>cluster</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Freq</t>
-  </si>
-  <si>
-    <t>RelFreq</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Regime</t>
-  </si>
-  <si>
-    <t>NonPerennial</t>
-  </si>
-  <si>
-    <t>Perennial</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Tributaries</t>
-  </si>
-  <si>
-    <t>Main Stem</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelFreq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonPerennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tributaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -115,25 +105,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -415,14 +393,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -449,14 +424,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>69</v>
       </c>
-      <c r="E2" s="2">
-        <v>56.557377049180303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E2" t="n">
+        <v>56.5573770491803</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -466,14 +441,14 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="2">
-        <v>16.393442622950801</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E3" t="n">
+        <v>16.3934426229508</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -483,14 +458,14 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>33</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" t="n">
         <v>27.0491803278689</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -500,14 +475,14 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2">
-        <v>35.714285714285701</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35.7142857142857</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -517,14 +492,14 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="2">
-        <v>64.285714285714306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E6" t="n">
+        <v>64.2857142857143</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -534,14 +509,14 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="2">
-        <v>31.496062992125999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E7" t="n">
+        <v>31.496062992126</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -551,14 +526,14 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>29</v>
       </c>
-      <c r="E8" s="2">
-        <v>22.834645669291302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E8" t="n">
+        <v>22.8346456692913</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -568,14 +543,14 @@
       <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>58</v>
       </c>
-      <c r="E9" s="2">
-        <v>45.669291338582703</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E9" t="n">
+        <v>45.6692913385827</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -585,14 +560,14 @@
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="2">
-        <v>10.752688172042999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E10" t="n">
+        <v>10.752688172043</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -602,14 +577,14 @@
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>54</v>
       </c>
-      <c r="E11" s="2">
-        <v>58.064516129032299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E11" t="n">
+        <v>58.0645161290323</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -619,14 +594,14 @@
       <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>29</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" t="n">
         <v>31.1827956989247</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -636,14 +611,14 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1">
-        <v>4.0983606557377001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.0983606557377</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -653,14 +628,14 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>117</v>
       </c>
-      <c r="E14" s="2">
-        <v>95.901639344262307</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E14" t="n">
+        <v>95.9016393442623</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -670,14 +645,14 @@
       <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>13</v>
       </c>
-      <c r="E15" s="2">
-        <v>92.857142857142904</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E15" t="n">
+        <v>92.8571428571429</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -687,14 +662,14 @@
       <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="1">
-        <v>7.1428571428571397</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E16" t="n">
+        <v>7.14285714285714</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -704,14 +679,14 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>127</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -721,14 +696,14 @@
       <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>29</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" t="n">
         <v>31.1827956989247</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -738,14 +713,14 @@
       <c r="C19" t="s">
         <v>15</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>64</v>
       </c>
-      <c r="E19" s="2">
-        <v>68.817204301075293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E19" t="n">
+        <v>68.8172043010753</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -755,14 +730,14 @@
       <c r="C20" t="s">
         <v>17</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>122</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -772,14 +747,14 @@
       <c r="C21" t="s">
         <v>17</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>14</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -789,14 +764,14 @@
       <c r="C22" t="s">
         <v>18</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>97</v>
       </c>
-      <c r="E22" s="2">
-        <v>76.377952755905497</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E22" t="n">
+        <v>76.3779527559055</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -806,14 +781,14 @@
       <c r="C23" t="s">
         <v>17</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>30</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" t="n">
         <v>23.6220472440945</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -823,14 +798,14 @@
       <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>9</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" t="n">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -840,15 +815,15 @@
       <c r="C25" t="s">
         <v>17</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>84</v>
       </c>
-      <c r="E25" s="2">
-        <v>90.322580645161295</v>
+      <c r="E25" t="n">
+        <v>90.3225806451613</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Zinc/5. Cluster analysis/Typology Plots/Relative_freq_percentages_by_cluster.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Relative_freq_percentages_by_cluster.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">Variable</t>
   </si>
   <si>
-    <t xml:space="preserve">cluster</t>
+    <t xml:space="preserve">cluster4</t>
   </si>
   <si>
     <t xml:space="preserve">Value</t>
